--- a/output/pdf_financials_xlsx/ZNX.xlsx
+++ b/output/pdf_financials_xlsx/ZNX.xlsx
@@ -5971,52 +5971,52 @@
         <v>8.406347999999999</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>8.226203</v>
+        <v>8.053851</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>9.260407000000001</v>
+        <v>11.1509</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>11.599747</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>11.931251</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>12.289609</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>13.00422</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>13.063384</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>13.700878</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>14.472792</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>14.893488</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>15.130102</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>15.127105</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>15.125609</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>15.125609</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>15.4315</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>15.812571</v>
       </c>
     </row>
     <row r="93">
@@ -9956,7 +9956,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -10597,7 +10601,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -11680,7 +11688,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -12878,7 +12890,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -16378,7 +16394,11 @@
           <t>Reserves 14</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -17033,7 +17053,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ZNX.xlsx
+++ b/output/pdf_financials_xlsx/ZNX.xlsx
@@ -1041,43 +1041,43 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.197038</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.189657</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.166637</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.093583</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.093179</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.105782</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.09339</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.050771</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.036968</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.012963</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.033671</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.064487</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.034142</v>
       </c>
     </row>
     <row r="13">
@@ -2003,43 +2003,43 @@
         <v>-1.664961</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.627873</v>
+        <v>-1.824911</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.333934</v>
+        <v>-2.523591</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.337398</v>
+        <v>-2.504035</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-2.998941</v>
+        <v>-3.092524</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-2.550399</v>
+        <v>-2.643578</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.189017</v>
+        <v>-2.294799</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-2.011776</v>
+        <v>-2.105166</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.246987</v>
+        <v>-1.297758</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.7675419999999999</v>
+        <v>-0.8045099999999999</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.86399</v>
+        <v>-0.876953</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.564665</v>
+        <v>-0.598336</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.8887389999999999</v>
+        <v>-0.953226</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.806971</v>
+        <v>-0.841113</v>
       </c>
     </row>
     <row r="28">
@@ -2119,43 +2119,43 @@
         <v>-1.659575</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.622214</v>
+        <v>-1.819252</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.328996</v>
+        <v>-2.518653</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.331066</v>
+        <v>-2.497703</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.992646</v>
+        <v>-3.086229</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.546675</v>
+        <v>-2.639854</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.18636</v>
+        <v>-2.292142</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.009338</v>
+        <v>-2.102728</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.244366</v>
+        <v>-1.295137</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.76466</v>
+        <v>-0.801628</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.86399</v>
+        <v>-0.876953</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.564665</v>
+        <v>-0.598336</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.8887389999999999</v>
+        <v>-0.953226</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.806971</v>
+        <v>-0.841113</v>
       </c>
     </row>
     <row r="30">
@@ -2429,40 +2429,40 @@
         <v>13.028707</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>10.558472</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>9.068599000000001</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.550103</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>4.464425</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.14888</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.802671</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.208938</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>3.066527</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.804822</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.25502</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.6885520000000001</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.705861</v>
       </c>
     </row>
     <row r="35">
@@ -2545,40 +2545,40 @@
         <v>14.107687</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.255796</v>
+        <v>10.814268</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.048245</v>
+        <v>9.116844</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.09039999999999999</v>
+        <v>2.640503</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.116442</v>
+        <v>4.580867</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.05715</v>
+        <v>1.20603</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.041875</v>
+        <v>0.844546</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.033625</v>
+        <v>0.242563</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>3.066527</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.804822</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>1.25502</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.6885520000000001</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.705861</v>
       </c>
     </row>
     <row r="37">
@@ -3241,40 +3241,40 @@
         <v>0.836358</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>10.888505</v>
+        <v>0.330033</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>10.129847</v>
+        <v>1.061248</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>6.623873</v>
+        <v>4.07377</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>8.732789</v>
+        <v>4.268364</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>5.337099</v>
+        <v>4.188219</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>3.387772</v>
+        <v>2.585101</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.672651</v>
+        <v>2.463713</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>3.101727</v>
+        <v>0.0352</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.86631</v>
+        <v>0.061488</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1.289053</v>
+        <v>0.034033</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.713347</v>
+        <v>0.024795</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.722935</v>
+        <v>0.017074</v>
       </c>
     </row>
     <row r="49">
@@ -7836,13 +7836,13 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0375</v>
       </c>
       <c r="P124" s="3" t="n">
         <v>0</v>
@@ -7894,13 +7894,13 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0375</v>
       </c>
       <c r="P125" s="3" t="n">
         <v>0</v>
@@ -8671,7 +8671,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13397,7 +13397,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -27815,7 +27815,11 @@
           <t>Lease payments 6</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -30413,7 +30417,11 @@
           <t>Lease payments 8</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -34098,7 +34106,11 @@
           <t>Lease payments 9</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
@@ -44314,7 +44326,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -45308,7 +45320,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -46300,7 +46312,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -46916,7 +46928,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -47920,7 +47932,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -48928,7 +48940,7 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -50902,7 +50914,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -51389,7 +51401,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -59696,7 +59708,7 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">

--- a/output/pdf_financials_xlsx/ZNX.xlsx
+++ b/output/pdf_financials_xlsx/ZNX.xlsx
@@ -2082,13 +2082,13 @@
         <v>0.002438</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.002621</v>
+        <v>0.083592</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.002882</v>
+        <v>0.084594</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.035545</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>0</v>
@@ -2140,13 +2140,13 @@
         <v>-2.102728</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.295137</v>
+        <v>-1.214166</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.801628</v>
+        <v>-0.719916</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.876953</v>
+        <v>-0.841408</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-0.598336</v>
@@ -6444,13 +6444,13 @@
         <v>0</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.083592</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.084594</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.035545</v>
       </c>
       <c r="P100" s="3" t="n">
         <v>0</v>
@@ -27112,7 +27112,11 @@
           <t>Depreciation of the right-of-use asset 6</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -28324,7 +28328,11 @@
           <t>Depreciation of the right-of-use asset 8</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -32411,7 +32419,11 @@
           <t>Depreciation of the right-of-use asset 9</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -47629,7 +47641,11 @@
           <t>Depreciation of the right-of-use asset 6</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E396" t="inlineStr">
         <is>
           <t>-</t>
@@ -48742,7 +48758,11 @@
           <t>Depreciation of the right-of-use asset 8</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E407" t="inlineStr">
         <is>
           <t>-</t>
@@ -52892,7 +52912,11 @@
           <t>Depreciation of the right-of-use asset 9</t>
         </is>
       </c>
-      <c r="D449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E449" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ZNX.xlsx
+++ b/output/pdf_financials_xlsx/ZNX.xlsx
@@ -745,31 +745,31 @@
         <v>0.289125</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.546554</v>
+        <v>0.549554</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.733079</v>
+        <v>0.783079</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.627214</v>
+        <v>0.677214</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.501988</v>
+        <v>0.551988</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.566551</v>
+        <v>0.616551</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.578254</v>
+        <v>0.618254</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.6225889999999999</v>
+        <v>0.662589</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.574967</v>
+        <v>0.614967</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.823508</v>
+        <v>0.843508</v>
       </c>
       <c r="M7" s="3" t="n">
         <v>0.399333</v>
@@ -919,13 +919,13 @@
         <v>1.039987</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.45371</v>
+        <v>1.45671</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1.23787</v>
+        <v>1.28787</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.05218</v>
+        <v>1.10218</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>2.329228</v>
@@ -980,10 +980,10 @@
         <v>-3.479102</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-1.23787</v>
+        <v>-1.28787</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-1.05218</v>
+        <v>-1.10218</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>-2.329228</v>
@@ -1325,7 +1325,7 @@
         <v>5.525814</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.963093</v>
+        <v>-0.288742</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0.074305</v>
@@ -1334,31 +1334,31 @@
         <v>0.233993</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.011223</v>
+        <v>-0.011223</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.416938</v>
+        <v>-0.416938</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.027725</v>
+        <v>-0.027725</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.5230860000000001</v>
+        <v>-0.5230860000000001</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.370034</v>
+        <v>-0.370034</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.356174</v>
+        <v>-0.356174</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>0.046445</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>0.033992</v>
+        <v>-0.033992</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>-0.8716</v>
+        <v>-0.02</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>-0</v>
@@ -2263,7 +2263,7 @@
         <v>-37.54225174129623</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-28.72394776265633</v>
+        <v>-8.611639919389836</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-4.462867298393176</v>
@@ -2296,7 +2296,7 @@
         <v>-4.428682730065586</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>-100.8807972314494</v>
+        <v>-2.314841606963043</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>-0</v>
@@ -7091,13 +7091,13 @@
         <v>0</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003026</v>
       </c>
       <c r="Q111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001263</v>
       </c>
       <c r="R111" s="3" t="n">
-        <v>0</v>
+        <v>-0.015162</v>
       </c>
     </row>
     <row r="112">
@@ -7317,7 +7317,7 @@
         <v>0</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.108178</v>
       </c>
       <c r="O115" s="3" t="n">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         <v>0</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003026</v>
       </c>
       <c r="Q134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001263</v>
       </c>
       <c r="R134" s="3" t="n">
-        <v>0</v>
+        <v>-0.015162</v>
       </c>
     </row>
     <row r="135">
@@ -8517,13 +8517,13 @@
         <v>-2.220955</v>
       </c>
       <c r="P135" s="3" t="n">
-        <v>-0.546776</v>
+        <v>-0.549802</v>
       </c>
       <c r="Q135" s="3" t="n">
-        <v>-0.529905</v>
+        <v>-0.531168</v>
       </c>
       <c r="R135" s="3" t="n">
-        <v>-0.467529</v>
+        <v>-0.482691</v>
       </c>
     </row>
   </sheetData>
@@ -25031,7 +25031,11 @@
           <t>Purchase of equipment 7</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -29124,7 +29128,11 @@
           <t>Deferred income tax recovery 14</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -31631,7 +31639,11 @@
           <t>Proceeds from sale of marketable securities, net 4</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -33229,7 +33241,11 @@
           <t>Deferred income tax recovery 15</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -34714,7 +34730,11 @@
           <t>Deferred income tax recovery 9</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
           <t>-</t>
@@ -37167,7 +37187,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -50528,7 +50552,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D425" t="inlineStr"/>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E425" t="inlineStr">
         <is>
           <t>-</t>
@@ -53017,7 +53045,11 @@
           <t>Directors fees 17</t>
         </is>
       </c>
-      <c r="D450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E450" t="inlineStr">
         <is>
           <t>-</t>
@@ -54197,7 +54229,11 @@
           <t>Directors fees 15</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E462" t="inlineStr">
         <is>
           <t>-</t>
@@ -55450,7 +55486,11 @@
           <t>Deferred income tax recovery 13</t>
         </is>
       </c>
-      <c r="D475" t="inlineStr"/>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E475" t="inlineStr">
         <is>
           <t>-</t>
@@ -56600,7 +56640,11 @@
           <t>Directors fees 14</t>
         </is>
       </c>
-      <c r="D487" t="inlineStr"/>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E487" t="inlineStr">
         <is>
           <t>-</t>
@@ -57291,7 +57335,11 @@
           <t>Deferred income tax recovery 12</t>
         </is>
       </c>
-      <c r="D494" t="inlineStr"/>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E494" t="inlineStr">
         <is>
           <t>-</t>
@@ -60637,7 +60685,11 @@
           <t>Deferred income tax recovery (expense) 12</t>
         </is>
       </c>
-      <c r="D528" t="inlineStr"/>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E528" t="inlineStr">
         <is>
           <t>-</t>
@@ -62756,7 +62808,11 @@
           <t>Deferred income tax recovery 13</t>
         </is>
       </c>
-      <c r="D549" t="inlineStr"/>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E549" t="inlineStr">
         <is>
           <t>-</t>
@@ -63253,7 +63309,11 @@
           <t>Directors fees (Note 11)</t>
         </is>
       </c>
-      <c r="D554" t="inlineStr"/>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E554" t="inlineStr">
         <is>
           <t>-</t>
